--- a/DADOS.xlsx
+++ b/DADOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/GITHUB/PARAMETROS MINIMOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="500" documentId="11_C2318B871671820C540791CC0C0EFCB85A7F69AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BB34C04-656A-4D0C-95AE-47E7C66E1053}"/>
+  <xr:revisionPtr revIDLastSave="520" documentId="11_C2318B871671820C540791CC0C0EFCB85A7F69AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C5ABA7F-6B2D-4B87-9667-78C2E164606E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1771,11 +1771,25 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="125">
+  <dxfs count="87">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1818,292 +1832,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4137,7 +3865,7 @@
         <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>99</v>
@@ -4147,15 +3875,15 @@
       </c>
       <c r="F31" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G31" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H31" s="3" t="str">
         <f t="shared" si="2"/>
-        <v>Não instituída</v>
+        <v>Instituída</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>521</v>
@@ -6468,7 +6196,7 @@
         <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>182</v>
@@ -6478,10 +6206,10 @@
       </c>
       <c r="F31" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>183</v>
@@ -6491,7 +6219,7 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>522</v>
@@ -6534,7 +6262,7 @@
       </c>
       <c r="W31" s="3">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X31" s="3" t="s">
         <v>96</v>
@@ -6785,57 +6513,57 @@
     <mergeCell ref="W4:X4"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C34">
-    <cfRule type="expression" dxfId="124" priority="1">
+    <cfRule type="expression" dxfId="86" priority="1">
       <formula>C7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="123" priority="2">
+    <cfRule type="expression" dxfId="85" priority="2">
       <formula>C7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="3">
+    <cfRule type="expression" dxfId="84" priority="3">
       <formula>OR(C7="Não atende",C7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G34">
-    <cfRule type="expression" dxfId="121" priority="4">
+    <cfRule type="expression" dxfId="83" priority="4">
       <formula>G7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="5">
+    <cfRule type="expression" dxfId="82" priority="5">
       <formula>G7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="119" priority="6">
+    <cfRule type="expression" dxfId="81" priority="6">
       <formula>OR(G7="Não atende",G7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K34">
-    <cfRule type="expression" dxfId="118" priority="7">
+    <cfRule type="expression" dxfId="80" priority="7">
       <formula>K7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="8">
+    <cfRule type="expression" dxfId="79" priority="8">
       <formula>K7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="9">
+    <cfRule type="expression" dxfId="78" priority="9">
       <formula>OR(K7="Não atende",K7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O7:O34">
-    <cfRule type="expression" dxfId="115" priority="10">
+    <cfRule type="expression" dxfId="77" priority="10">
       <formula>O7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="11">
+    <cfRule type="expression" dxfId="76" priority="11">
       <formula>O7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="12">
+    <cfRule type="expression" dxfId="75" priority="12">
       <formula>OR(O7="Não atende",O7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S7:S34">
-    <cfRule type="expression" dxfId="112" priority="13">
+    <cfRule type="expression" dxfId="74" priority="13">
       <formula>S7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="111" priority="14">
+    <cfRule type="expression" dxfId="73" priority="14">
       <formula>S7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="15">
+    <cfRule type="expression" dxfId="72" priority="15">
       <formula>OR(S7="Não atende",S7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7987,7 +7715,7 @@
         <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>235</v>
@@ -7997,10 +7725,10 @@
       </c>
       <c r="F31" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>232</v>
@@ -8010,11 +7738,11 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K31" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>96</v>
@@ -8154,24 +7882,24 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C34">
-    <cfRule type="expression" dxfId="109" priority="1">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>C7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="2">
+    <cfRule type="expression" dxfId="70" priority="2">
       <formula>C7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="3">
+    <cfRule type="expression" dxfId="69" priority="3">
       <formula>OR(C7="Não atende",C7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G34">
-    <cfRule type="expression" dxfId="106" priority="4">
+    <cfRule type="expression" dxfId="68" priority="4">
       <formula>G7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="5">
+    <cfRule type="expression" dxfId="67" priority="5">
       <formula>G7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="6">
+    <cfRule type="expression" dxfId="66" priority="6">
       <formula>OR(G7="Não atende",G7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10733,7 +10461,7 @@
         <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>73</v>
@@ -10743,10 +10471,10 @@
       </c>
       <c r="F31" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>73</v>
@@ -10756,10 +10484,10 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>73</v>
@@ -10769,10 +10497,10 @@
       </c>
       <c r="N31" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P31" s="5" t="s">
         <v>278</v>
@@ -10782,10 +10510,10 @@
       </c>
       <c r="R31" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T31" s="5" t="s">
         <v>274</v>
@@ -10795,10 +10523,10 @@
       </c>
       <c r="V31" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="X31" s="5" t="s">
         <v>297</v>
@@ -10808,11 +10536,11 @@
       </c>
       <c r="Z31" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA31" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AB31" s="3" t="s">
         <v>96</v>
@@ -11109,68 +10837,68 @@
     <mergeCell ref="AA4:AB4"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C34">
-    <cfRule type="expression" dxfId="103" priority="1">
+    <cfRule type="expression" dxfId="65" priority="1">
       <formula>C7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="2">
+    <cfRule type="expression" dxfId="64" priority="2">
       <formula>C7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="3">
+    <cfRule type="expression" dxfId="63" priority="3">
       <formula>OR(C7="Não atende",C7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G34">
-    <cfRule type="expression" dxfId="100" priority="4">
+    <cfRule type="expression" dxfId="62" priority="4">
       <formula>G7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="5">
+    <cfRule type="expression" dxfId="61" priority="5">
       <formula>G7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="6">
+    <cfRule type="expression" dxfId="60" priority="6">
       <formula>OR(G7="Não atende",G7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K34">
-    <cfRule type="expression" dxfId="97" priority="7">
+    <cfRule type="expression" dxfId="59" priority="7">
       <formula>K7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="8">
+    <cfRule type="expression" dxfId="58" priority="8">
       <formula>K7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="95" priority="9">
+    <cfRule type="expression" dxfId="57" priority="9">
       <formula>OR(K7="Não atende",K7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O7:O34">
-    <cfRule type="expression" dxfId="94" priority="10">
+    <cfRule type="expression" dxfId="56" priority="10">
       <formula>O7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="11">
+    <cfRule type="expression" dxfId="55" priority="11">
       <formula>O7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="12">
+    <cfRule type="expression" dxfId="54" priority="12">
       <formula>OR(O7="Não atende",O7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S7:S34">
-    <cfRule type="expression" dxfId="91" priority="13">
+    <cfRule type="expression" dxfId="53" priority="13">
       <formula>S7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="14">
+    <cfRule type="expression" dxfId="52" priority="14">
       <formula>S7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="15">
+    <cfRule type="expression" dxfId="51" priority="15">
       <formula>OR(S7="Não atende",S7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W7:W34">
-    <cfRule type="expression" dxfId="88" priority="16">
+    <cfRule type="expression" dxfId="50" priority="16">
       <formula>W7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="87" priority="17">
+    <cfRule type="expression" dxfId="49" priority="17">
       <formula>W7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="18">
+    <cfRule type="expression" dxfId="48" priority="18">
       <formula>OR(W7="Não atende",W7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12322,7 +12050,7 @@
         <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>313</v>
@@ -12332,10 +12060,10 @@
       </c>
       <c r="F31" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>317</v>
@@ -12345,11 +12073,11 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K31" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>96</v>
@@ -12489,24 +12217,24 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C34">
-    <cfRule type="expression" dxfId="85" priority="1">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>C7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="2">
+    <cfRule type="expression" dxfId="46" priority="2">
       <formula>C7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="3">
+    <cfRule type="expression" dxfId="45" priority="3">
       <formula>OR(C7="Não atende",C7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G34">
-    <cfRule type="expression" dxfId="82" priority="4">
+    <cfRule type="expression" dxfId="44" priority="4">
       <formula>G7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="5">
+    <cfRule type="expression" dxfId="43" priority="5">
       <formula>G7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="6">
+    <cfRule type="expression" dxfId="42" priority="6">
       <formula>OR(G7="Não atende",G7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15478,7 +15206,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="T31" s="5" t="s">
         <v>353</v>
@@ -15488,7 +15216,7 @@
       </c>
       <c r="V31" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W31" s="3" t="s">
         <v>524</v>
@@ -15504,7 +15232,7 @@
         <v>0</v>
       </c>
       <c r="AA31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AB31" s="5" t="s">
         <v>353</v>
@@ -15514,11 +15242,11 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE31" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF31" s="3" t="s">
         <v>96</v>
@@ -15857,79 +15585,79 @@
     <mergeCell ref="AE4:AF4"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C34">
-    <cfRule type="expression" dxfId="79" priority="91">
+    <cfRule type="expression" dxfId="41" priority="91">
       <formula>C7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="92">
+    <cfRule type="expression" dxfId="40" priority="92">
       <formula>C7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="93">
+    <cfRule type="expression" dxfId="39" priority="93">
       <formula>OR(C7="Não atende",C7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G34">
-    <cfRule type="expression" dxfId="76" priority="64">
+    <cfRule type="expression" dxfId="38" priority="64">
       <formula>G7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="65">
+    <cfRule type="expression" dxfId="37" priority="65">
       <formula>G7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="66">
+    <cfRule type="expression" dxfId="36" priority="66">
       <formula>OR(G7="Não atende",G7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K34">
-    <cfRule type="expression" dxfId="73" priority="61">
+    <cfRule type="expression" dxfId="35" priority="61">
       <formula>K7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="62">
+    <cfRule type="expression" dxfId="34" priority="62">
       <formula>K7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="63">
+    <cfRule type="expression" dxfId="33" priority="63">
       <formula>OR(K7="Não atende",K7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O7:O34">
-    <cfRule type="expression" dxfId="70" priority="46">
+    <cfRule type="expression" dxfId="32" priority="46">
       <formula>O7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="47">
+    <cfRule type="expression" dxfId="31" priority="47">
       <formula>O7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="48">
+    <cfRule type="expression" dxfId="30" priority="48">
       <formula>OR(O7="Não atende",O7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S7:S34">
-    <cfRule type="expression" dxfId="67" priority="25">
+    <cfRule type="expression" dxfId="29" priority="25">
       <formula>S7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="26">
+    <cfRule type="expression" dxfId="28" priority="26">
       <formula>S7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="27">
+    <cfRule type="expression" dxfId="27" priority="27">
       <formula>OR(S7="Não atende",S7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W7:W34">
-    <cfRule type="expression" dxfId="64" priority="13">
+    <cfRule type="expression" dxfId="26" priority="13">
       <formula>W7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="14">
+    <cfRule type="expression" dxfId="25" priority="14">
       <formula>W7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="15">
+    <cfRule type="expression" dxfId="24" priority="15">
       <formula>OR(W7="Não atende",W7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA7:AA34">
-    <cfRule type="expression" dxfId="61" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>AA7="Atende"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="2">
+    <cfRule type="expression" dxfId="22" priority="2">
       <formula>AA7="Parcial"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="3">
+    <cfRule type="expression" dxfId="21" priority="3">
       <formula>OR(AA7="Não atende",AA7="Sem evidência")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18128,7 +17856,7 @@
         <v>404</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>418</v>
@@ -18137,7 +17865,7 @@
         <v>406</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="M31" s="5" t="s">
         <v>476</v>
@@ -18155,7 +17883,7 @@
         <v>410</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="S31" s="5" t="s">
         <v>494</v>
@@ -18164,7 +17892,7 @@
         <v>412</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="V31" s="5" t="s">
         <v>442</v>
@@ -18174,7 +17902,7 @@
       </c>
       <c r="X31" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y31" s="3" t="s">
         <v>96</v>
@@ -18430,212 +18158,80 @@
     <mergeCell ref="X4:Y4"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C34">
-    <cfRule type="expression" dxfId="58" priority="37">
+    <cfRule type="expression" dxfId="20" priority="37">
       <formula>C7="Sim"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="38">
+    <cfRule type="expression" dxfId="19" priority="38">
       <formula>C7="Não"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="39">
+    <cfRule type="expression" dxfId="18" priority="39">
       <formula>C7="Sem evidência"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F34">
-    <cfRule type="expression" dxfId="55" priority="40">
+    <cfRule type="expression" dxfId="17" priority="40">
       <formula>F7="Sim"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="41">
+    <cfRule type="expression" dxfId="16" priority="41">
       <formula>F7="Não"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="42">
+    <cfRule type="expression" dxfId="15" priority="42">
       <formula>F7="Sem evidência"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:I34">
-    <cfRule type="expression" dxfId="52" priority="43">
+    <cfRule type="expression" dxfId="14" priority="43">
       <formula>I7="Sim"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="44">
+    <cfRule type="expression" dxfId="13" priority="44">
       <formula>I7="Não"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="45">
+    <cfRule type="expression" dxfId="12" priority="45">
       <formula>I7="Sem evidência"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:L34">
-    <cfRule type="expression" dxfId="49" priority="46">
+    <cfRule type="expression" dxfId="11" priority="46">
       <formula>L7="Sim"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="47">
+    <cfRule type="expression" dxfId="10" priority="47">
       <formula>L7="Não"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="48">
+    <cfRule type="expression" dxfId="9" priority="48">
       <formula>L7="Sem evidência"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O30 O32 O7:O28">
-    <cfRule type="expression" dxfId="46" priority="49">
+  <conditionalFormatting sqref="O7:O34">
+    <cfRule type="expression" dxfId="8" priority="27">
+      <formula>O7="Sem evidência"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="25">
       <formula>O7="Sim"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="50">
+    <cfRule type="expression" dxfId="6" priority="26">
       <formula>O7="Não"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="51">
-      <formula>O7="Sem evidência"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R7:R34">
+    <cfRule type="expression" dxfId="5" priority="15">
+      <formula>R7="Sem evidência"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="13">
+      <formula>R7="Sim"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="14">
+      <formula>R7="Não"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R30 R32 R7:R28">
-    <cfRule type="expression" dxfId="43" priority="52">
-      <formula>R7="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="53">
-      <formula>R7="Não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="41" priority="54">
-      <formula>R7="Sem evidência"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U30 U32 U7:U28">
-    <cfRule type="expression" dxfId="40" priority="55">
-      <formula>U7="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="39" priority="56">
+  <conditionalFormatting sqref="U7:U34">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>U7="Não"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="57">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>U7="Sem evidência"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O29">
-    <cfRule type="expression" dxfId="35" priority="34">
-      <formula>O29="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="35">
-      <formula>O29="Não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="36">
-      <formula>O29="Sem evidência"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O31">
-    <cfRule type="expression" dxfId="32" priority="31">
-      <formula>O31="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="32">
-      <formula>O31="Não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="33">
-      <formula>O31="Sem evidência"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O33">
-    <cfRule type="expression" dxfId="29" priority="28">
-      <formula>O33="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="29">
-      <formula>O33="Não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="30">
-      <formula>O33="Sem evidência"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O34">
-    <cfRule type="expression" dxfId="26" priority="25">
-      <formula>O34="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="26">
-      <formula>O34="Não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="27">
-      <formula>O34="Sem evidência"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R29">
-    <cfRule type="expression" dxfId="23" priority="22">
-      <formula>R29="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="23">
-      <formula>R29="Não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="24">
-      <formula>R29="Sem evidência"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R31">
-    <cfRule type="expression" dxfId="20" priority="19">
-      <formula>R31="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="20">
-      <formula>R31="Não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="21">
-      <formula>R31="Sem evidência"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R33">
-    <cfRule type="expression" dxfId="17" priority="16">
-      <formula>R33="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="17">
-      <formula>R33="Não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="18">
-      <formula>R33="Sem evidência"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R34">
-    <cfRule type="expression" dxfId="14" priority="13">
-      <formula>R34="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="14">
-      <formula>R34="Não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="15">
-      <formula>R34="Sem evidência"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U29">
-    <cfRule type="expression" dxfId="11" priority="10">
-      <formula>U29="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="11">
-      <formula>U29="Não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="12">
-      <formula>U29="Sem evidência"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U31">
-    <cfRule type="expression" dxfId="8" priority="7">
-      <formula>U31="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>U31="Não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="9">
-      <formula>U31="Sem evidência"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U33">
-    <cfRule type="expression" dxfId="5" priority="4">
-      <formula>U33="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>U33="Não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6">
-      <formula>U33="Sem evidência"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U34">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>U34="Sim"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>U34="Não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>U34="Sem evidência"</formula>
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>U7="Sim"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -18904,7 +18500,7 @@
       </c>
       <c r="S6">
         <f>COUNTIF(M5:M32,"Instituída")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -18975,10 +18571,10 @@
       </c>
       <c r="S7">
         <f>COUNTIF(M5:M32,"Não instituída")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>105</v>
       </c>
@@ -19188,7 +18784,7 @@
       </c>
       <c r="S10">
         <f>COUNTIF(O5:O32,"*satisfatória*")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -20293,7 +19889,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>147</v>
       </c>
@@ -20366,62 +19962,62 @@
       </c>
       <c r="C29" s="3">
         <f>'01_Institucionalização'!G31</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D29" s="3">
         <f>'02_Autonomia'!W31</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E29" s="3">
         <f>'03_Imparcialidade'!K31</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F29" s="3">
         <f>'04_Acessibilidade'!AA31</f>
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="G29" s="3">
         <f>'05_Transparência'!K31</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H29" s="3">
         <f>'06_Integração Tec'!AE31</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="3" t="str">
+        <v>4</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="0"/>
+        <v>77.5</v>
+      </c>
+      <c r="J29" s="3">
         <f>IF(M29&lt;&gt;"Instituída","",'07_Maturidade'!X31)</f>
-        <v/>
-      </c>
-      <c r="K29" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="K29" s="3">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L29" s="3" t="str">
+        <v>5</v>
+      </c>
+      <c r="L29" s="3">
         <f t="shared" si="2"/>
-        <v/>
+        <v>82.5</v>
       </c>
       <c r="M29" s="3" t="str">
         <f>'01_Institucionalização'!H31</f>
-        <v>Não instituída</v>
+        <v>Instituída</v>
       </c>
       <c r="N29" s="3" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>Não</v>
       </c>
       <c r="O29" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Não instituída</v>
+        <v>Instituída — aderência satisfatória</v>
       </c>
       <c r="P29" s="3" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+        <v>Bônus integralmente aplicado</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>151</v>
       </c>

--- a/DADOS.xlsx
+++ b/DADOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/GITHUB/PARAMETROS MINIMOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="520" documentId="11_C2318B871671820C540791CC0C0EFCB85A7F69AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C5ABA7F-6B2D-4B87-9667-78C2E164606E}"/>
+  <xr:revisionPtr revIDLastSave="523" documentId="11_C2318B871671820C540791CC0C0EFCB85A7F69AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDBF98C4-2906-4A1F-8597-21E0CDC6E6F6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Metodologia" sheetId="1" r:id="rId1"/>
@@ -1621,10 +1621,6 @@
     <t>Baixa/insuficiente aderência</t>
   </si>
   <si>
-    <t>Doc. SEI 37070578
-Informou que ainda está em tramitação</t>
-  </si>
-  <si>
     <t>Atende</t>
   </si>
   <si>
@@ -1635,6 +1631,9 @@
   </si>
   <si>
     <t>Parcial</t>
+  </si>
+  <si>
+    <t>Decreto</t>
   </si>
 </sst>
 </file>
@@ -1775,21 +1774,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1832,6 +1817,20 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3857,7 +3856,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>149</v>
       </c>
@@ -3886,7 +3885,7 @@
         <v>Instituída</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="24" x14ac:dyDescent="0.3">
@@ -4276,7 +4275,7 @@
         <v>98</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>182</v>
@@ -4289,7 +4288,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>183</v>
@@ -4302,7 +4301,7 @@
         <v>3</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>184</v>
@@ -4315,7 +4314,7 @@
         <v>3</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>185</v>
@@ -4328,7 +4327,7 @@
         <v>1.5</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>186</v>
@@ -4356,7 +4355,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>182</v>
@@ -4369,7 +4368,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>183</v>
@@ -4382,7 +4381,7 @@
         <v>3</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>187</v>
@@ -4395,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>188</v>
@@ -4408,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T8" s="5" t="s">
         <v>189</v>
@@ -4436,7 +4435,7 @@
         <v>104</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>182</v>
@@ -4449,7 +4448,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>183</v>
@@ -4462,7 +4461,7 @@
         <v>3</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>190</v>
@@ -4475,7 +4474,7 @@
         <v>3</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P9" s="5" t="s">
         <v>191</v>
@@ -4488,7 +4487,7 @@
         <v>3</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>189</v>
@@ -4516,7 +4515,7 @@
         <v>106</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>182</v>
@@ -4529,7 +4528,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>183</v>
@@ -4542,7 +4541,7 @@
         <v>3</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>192</v>
@@ -4555,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>191</v>
@@ -4568,7 +4567,7 @@
         <v>3</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T10" s="5" t="s">
         <v>189</v>
@@ -4596,7 +4595,7 @@
         <v>108</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>182</v>
@@ -4609,7 +4608,7 @@
         <v>3</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>183</v>
@@ -4622,7 +4621,7 @@
         <v>3</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>193</v>
@@ -4635,7 +4634,7 @@
         <v>3</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>191</v>
@@ -4648,7 +4647,7 @@
         <v>3</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T11" s="5" t="s">
         <v>189</v>
@@ -4676,7 +4675,7 @@
         <v>110</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>182</v>
@@ -4689,7 +4688,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>183</v>
@@ -4702,7 +4701,7 @@
         <v>3</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>192</v>
@@ -4715,7 +4714,7 @@
         <v>3</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P12" s="5" t="s">
         <v>191</v>
@@ -4728,7 +4727,7 @@
         <v>3</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T12" s="5" t="s">
         <v>189</v>
@@ -4756,7 +4755,7 @@
         <v>112</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>182</v>
@@ -4769,7 +4768,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>183</v>
@@ -4782,7 +4781,7 @@
         <v>3</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>194</v>
@@ -4795,7 +4794,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P13" s="5" t="s">
         <v>191</v>
@@ -4808,7 +4807,7 @@
         <v>3</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T13" s="5" t="s">
         <v>189</v>
@@ -4836,7 +4835,7 @@
         <v>114</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>182</v>
@@ -4849,7 +4848,7 @@
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>183</v>
@@ -4862,7 +4861,7 @@
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>195</v>
@@ -4875,7 +4874,7 @@
         <v>3</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P14" s="5" t="s">
         <v>191</v>
@@ -4888,7 +4887,7 @@
         <v>3</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T14" s="5" t="s">
         <v>189</v>
@@ -4916,7 +4915,7 @@
         <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>182</v>
@@ -4929,7 +4928,7 @@
         <v>3</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>183</v>
@@ -4942,7 +4941,7 @@
         <v>3</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>196</v>
@@ -4955,7 +4954,7 @@
         <v>3</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>191</v>
@@ -4968,7 +4967,7 @@
         <v>3</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T15" s="5" t="s">
         <v>189</v>
@@ -4996,7 +4995,7 @@
         <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>182</v>
@@ -5009,7 +5008,7 @@
         <v>3</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>183</v>
@@ -5022,7 +5021,7 @@
         <v>3</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>197</v>
@@ -5035,7 +5034,7 @@
         <v>3</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P16" s="5" t="s">
         <v>191</v>
@@ -5048,7 +5047,7 @@
         <v>3</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T16" s="5" t="s">
         <v>189</v>
@@ -5076,7 +5075,7 @@
         <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>182</v>
@@ -5089,7 +5088,7 @@
         <v>3</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>183</v>
@@ -5102,7 +5101,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>198</v>
@@ -5115,7 +5114,7 @@
         <v>3</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P17" s="5" t="s">
         <v>191</v>
@@ -5128,7 +5127,7 @@
         <v>3</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T17" s="5" t="s">
         <v>189</v>
@@ -5156,7 +5155,7 @@
         <v>121</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>182</v>
@@ -5169,7 +5168,7 @@
         <v>3</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>183</v>
@@ -5182,7 +5181,7 @@
         <v>3</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>199</v>
@@ -5195,7 +5194,7 @@
         <v>3</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P18" s="5" t="s">
         <v>191</v>
@@ -5208,7 +5207,7 @@
         <v>3</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T18" s="5" t="s">
         <v>189</v>
@@ -5236,7 +5235,7 @@
         <v>123</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>182</v>
@@ -5249,7 +5248,7 @@
         <v>3</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>183</v>
@@ -5262,7 +5261,7 @@
         <v>3</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>187</v>
@@ -5275,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P19" s="5" t="s">
         <v>191</v>
@@ -5288,7 +5287,7 @@
         <v>3</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T19" s="5" t="s">
         <v>189</v>
@@ -5316,7 +5315,7 @@
         <v>126</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>200</v>
@@ -5329,7 +5328,7 @@
         <v>3</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>201</v>
@@ -5342,7 +5341,7 @@
         <v>3</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>202</v>
@@ -5355,7 +5354,7 @@
         <v>3</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P20" s="5" t="s">
         <v>191</v>
@@ -5368,7 +5367,7 @@
         <v>3</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T20" s="5" t="s">
         <v>189</v>
@@ -5396,7 +5395,7 @@
         <v>128</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>203</v>
@@ -5409,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>204</v>
@@ -5422,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>205</v>
@@ -5435,7 +5434,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>206</v>
@@ -5448,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T21" s="5" t="s">
         <v>206</v>
@@ -5476,7 +5475,7 @@
         <v>131</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>182</v>
@@ -5489,7 +5488,7 @@
         <v>3</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>183</v>
@@ -5502,7 +5501,7 @@
         <v>3</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>207</v>
@@ -5515,7 +5514,7 @@
         <v>3</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>191</v>
@@ -5528,7 +5527,7 @@
         <v>3</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T22" s="5" t="s">
         <v>189</v>
@@ -5556,7 +5555,7 @@
         <v>133</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>182</v>
@@ -5569,7 +5568,7 @@
         <v>3</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>183</v>
@@ -5582,7 +5581,7 @@
         <v>3</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>187</v>
@@ -5595,7 +5594,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P23" s="5" t="s">
         <v>191</v>
@@ -5608,7 +5607,7 @@
         <v>3</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T23" s="5" t="s">
         <v>189</v>
@@ -5636,7 +5635,7 @@
         <v>135</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>182</v>
@@ -5649,7 +5648,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>183</v>
@@ -5662,7 +5661,7 @@
         <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>187</v>
@@ -5675,7 +5674,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P24" s="5" t="s">
         <v>191</v>
@@ -5688,7 +5687,7 @@
         <v>3</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T24" s="5" t="s">
         <v>189</v>
@@ -5716,7 +5715,7 @@
         <v>137</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>208</v>
@@ -5729,7 +5728,7 @@
         <v>3</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>183</v>
@@ -5742,7 +5741,7 @@
         <v>3</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>209</v>
@@ -5755,7 +5754,7 @@
         <v>3</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P25" s="5" t="s">
         <v>191</v>
@@ -5768,7 +5767,7 @@
         <v>3</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T25" s="5" t="s">
         <v>189</v>
@@ -5796,7 +5795,7 @@
         <v>139</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>182</v>
@@ -5809,7 +5808,7 @@
         <v>3</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>183</v>
@@ -5822,7 +5821,7 @@
         <v>3</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L26" s="5" t="s">
         <v>210</v>
@@ -5835,7 +5834,7 @@
         <v>3</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P26" s="5" t="s">
         <v>188</v>
@@ -5848,7 +5847,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T26" s="5" t="s">
         <v>189</v>
@@ -5876,7 +5875,7 @@
         <v>141</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>182</v>
@@ -5889,7 +5888,7 @@
         <v>3</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>183</v>
@@ -5902,7 +5901,7 @@
         <v>3</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L27" s="5" t="s">
         <v>193</v>
@@ -5915,7 +5914,7 @@
         <v>3</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P27" s="5" t="s">
         <v>191</v>
@@ -5928,7 +5927,7 @@
         <v>3</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T27" s="5" t="s">
         <v>189</v>
@@ -5956,7 +5955,7 @@
         <v>143</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>182</v>
@@ -5969,7 +5968,7 @@
         <v>3</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>204</v>
@@ -5982,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>211</v>
@@ -5995,7 +5994,7 @@
         <v>3</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P28" s="5" t="s">
         <v>191</v>
@@ -6008,7 +6007,7 @@
         <v>3</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T28" s="5" t="s">
         <v>189</v>
@@ -6036,7 +6035,7 @@
         <v>145</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>182</v>
@@ -6049,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>183</v>
@@ -6062,7 +6061,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>187</v>
@@ -6075,7 +6074,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="P29" s="5" t="s">
         <v>188</v>
@@ -6088,7 +6087,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T29" s="5" t="s">
         <v>189</v>
@@ -6116,7 +6115,7 @@
         <v>148</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>182</v>
@@ -6129,7 +6128,7 @@
         <v>3</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>183</v>
@@ -6142,7 +6141,7 @@
         <v>3</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>192</v>
@@ -6155,7 +6154,7 @@
         <v>3</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P30" s="5" t="s">
         <v>191</v>
@@ -6168,7 +6167,7 @@
         <v>3</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T30" s="5" t="s">
         <v>189</v>
@@ -6196,7 +6195,7 @@
         <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>182</v>
@@ -6209,7 +6208,7 @@
         <v>3</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>183</v>
@@ -6222,7 +6221,7 @@
         <v>3</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>212</v>
@@ -6235,7 +6234,7 @@
         <v>3</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P31" s="5" t="s">
         <v>191</v>
@@ -6248,7 +6247,7 @@
         <v>3</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T31" s="5" t="s">
         <v>189</v>
@@ -6276,7 +6275,7 @@
         <v>152</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>182</v>
@@ -6289,7 +6288,7 @@
         <v>3</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>183</v>
@@ -6302,7 +6301,7 @@
         <v>3</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>213</v>
@@ -6315,7 +6314,7 @@
         <v>3</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P32" s="5" t="s">
         <v>191</v>
@@ -6328,7 +6327,7 @@
         <v>3</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T32" s="5" t="s">
         <v>189</v>
@@ -6356,7 +6355,7 @@
         <v>154</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>155</v>
@@ -6369,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>155</v>
@@ -6382,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>155</v>
@@ -6406,7 +6405,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T33" s="5" t="s">
         <v>155</v>
@@ -6434,7 +6433,7 @@
         <v>157</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>203</v>
@@ -6447,7 +6446,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>183</v>
@@ -6460,7 +6459,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>187</v>
@@ -6731,7 +6730,7 @@
         <v>98</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>226</v>
@@ -6744,7 +6743,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>227</v>
@@ -6772,7 +6771,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>228</v>
@@ -6785,7 +6784,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>229</v>
@@ -6813,7 +6812,7 @@
         <v>104</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>230</v>
@@ -6826,7 +6825,7 @@
         <v>8</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>231</v>
@@ -6854,7 +6853,7 @@
         <v>106</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>228</v>
@@ -6867,7 +6866,7 @@
         <v>8</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>232</v>
@@ -6895,7 +6894,7 @@
         <v>108</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>233</v>
@@ -6908,7 +6907,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>231</v>
@@ -6936,7 +6935,7 @@
         <v>110</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>234</v>
@@ -6949,7 +6948,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>232</v>
@@ -6977,7 +6976,7 @@
         <v>112</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>235</v>
@@ -6990,7 +6989,7 @@
         <v>8</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>232</v>
@@ -7018,7 +7017,7 @@
         <v>114</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>236</v>
@@ -7031,7 +7030,7 @@
         <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>232</v>
@@ -7059,7 +7058,7 @@
         <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>237</v>
@@ -7072,7 +7071,7 @@
         <v>4</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>227</v>
@@ -7100,7 +7099,7 @@
         <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>238</v>
@@ -7113,7 +7112,7 @@
         <v>8</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>232</v>
@@ -7141,7 +7140,7 @@
         <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>239</v>
@@ -7154,7 +7153,7 @@
         <v>8</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>227</v>
@@ -7182,7 +7181,7 @@
         <v>121</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>240</v>
@@ -7195,7 +7194,7 @@
         <v>8</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>227</v>
@@ -7223,7 +7222,7 @@
         <v>123</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>228</v>
@@ -7236,7 +7235,7 @@
         <v>8</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>229</v>
@@ -7264,7 +7263,7 @@
         <v>126</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>241</v>
@@ -7277,7 +7276,7 @@
         <v>8</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>232</v>
@@ -7305,7 +7304,7 @@
         <v>128</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>242</v>
@@ -7318,7 +7317,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>243</v>
@@ -7346,7 +7345,7 @@
         <v>131</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>244</v>
@@ -7359,7 +7358,7 @@
         <v>8</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>229</v>
@@ -7387,7 +7386,7 @@
         <v>133</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>245</v>
@@ -7400,7 +7399,7 @@
         <v>8</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>231</v>
@@ -7428,7 +7427,7 @@
         <v>135</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>228</v>
@@ -7441,7 +7440,7 @@
         <v>8</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>232</v>
@@ -7469,7 +7468,7 @@
         <v>137</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>246</v>
@@ -7482,7 +7481,7 @@
         <v>8</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>227</v>
@@ -7510,7 +7509,7 @@
         <v>139</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>247</v>
@@ -7523,7 +7522,7 @@
         <v>8</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>232</v>
@@ -7551,7 +7550,7 @@
         <v>141</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>236</v>
@@ -7564,7 +7563,7 @@
         <v>8</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>227</v>
@@ -7592,7 +7591,7 @@
         <v>143</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>248</v>
@@ -7605,7 +7604,7 @@
         <v>8</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>227</v>
@@ -7633,7 +7632,7 @@
         <v>145</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>249</v>
@@ -7646,7 +7645,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>229</v>
@@ -7674,7 +7673,7 @@
         <v>148</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>228</v>
@@ -7687,7 +7686,7 @@
         <v>8</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>227</v>
@@ -7715,7 +7714,7 @@
         <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>235</v>
@@ -7728,7 +7727,7 @@
         <v>8</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>232</v>
@@ -7756,7 +7755,7 @@
         <v>152</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>250</v>
@@ -7769,7 +7768,7 @@
         <v>8</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>231</v>
@@ -7797,7 +7796,7 @@
         <v>154</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>155</v>
@@ -7810,7 +7809,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>155</v>
@@ -7838,7 +7837,7 @@
         <v>157</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>245</v>
@@ -7851,7 +7850,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>231</v>
@@ -8229,7 +8228,7 @@
         <v>98</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>73</v>
@@ -8242,7 +8241,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>20</v>
@@ -8255,7 +8254,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>73</v>
@@ -8268,7 +8267,7 @@
         <v>2</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>273</v>
@@ -8281,7 +8280,7 @@
         <v>3</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>274</v>
@@ -8294,7 +8293,7 @@
         <v>3</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X7" s="5" t="s">
         <v>275</v>
@@ -8322,7 +8321,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>73</v>
@@ -8335,7 +8334,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>73</v>
@@ -8348,7 +8347,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>73</v>
@@ -8361,7 +8360,7 @@
         <v>2</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>273</v>
@@ -8374,7 +8373,7 @@
         <v>3</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T8" s="5" t="s">
         <v>276</v>
@@ -8387,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X8" s="5" t="s">
         <v>277</v>
@@ -8415,7 +8414,7 @@
         <v>104</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>73</v>
@@ -8428,7 +8427,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>73</v>
@@ -8441,7 +8440,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>73</v>
@@ -8454,7 +8453,7 @@
         <v>2</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P9" s="5" t="s">
         <v>278</v>
@@ -8467,7 +8466,7 @@
         <v>1.5</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>274</v>
@@ -8480,7 +8479,7 @@
         <v>3</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X9" s="5" t="s">
         <v>279</v>
@@ -8508,7 +8507,7 @@
         <v>106</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>73</v>
@@ -8521,7 +8520,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>20</v>
@@ -8534,7 +8533,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>73</v>
@@ -8547,7 +8546,7 @@
         <v>2</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>278</v>
@@ -8560,7 +8559,7 @@
         <v>1.5</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T10" s="5" t="s">
         <v>274</v>
@@ -8573,7 +8572,7 @@
         <v>3</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X10" s="5" t="s">
         <v>280</v>
@@ -8601,7 +8600,7 @@
         <v>108</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>73</v>
@@ -8614,7 +8613,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>20</v>
@@ -8627,7 +8626,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>73</v>
@@ -8640,7 +8639,7 @@
         <v>2</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>278</v>
@@ -8653,7 +8652,7 @@
         <v>1.5</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T11" s="5" t="s">
         <v>281</v>
@@ -8666,7 +8665,7 @@
         <v>3</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X11" s="5" t="s">
         <v>282</v>
@@ -8694,7 +8693,7 @@
         <v>110</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>73</v>
@@ -8707,7 +8706,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>73</v>
@@ -8720,7 +8719,7 @@
         <v>2</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>73</v>
@@ -8733,7 +8732,7 @@
         <v>2</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P12" s="5" t="s">
         <v>273</v>
@@ -8746,7 +8745,7 @@
         <v>3</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T12" s="5" t="s">
         <v>274</v>
@@ -8759,7 +8758,7 @@
         <v>3</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X12" s="5" t="s">
         <v>283</v>
@@ -8787,7 +8786,7 @@
         <v>112</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>73</v>
@@ -8800,7 +8799,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>73</v>
@@ -8813,7 +8812,7 @@
         <v>2</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>20</v>
@@ -8826,7 +8825,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P13" s="5" t="s">
         <v>278</v>
@@ -8839,7 +8838,7 @@
         <v>1.5</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T13" s="5" t="s">
         <v>276</v>
@@ -8852,7 +8851,7 @@
         <v>0</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X13" s="5" t="s">
         <v>284</v>
@@ -8880,7 +8879,7 @@
         <v>114</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>73</v>
@@ -8893,7 +8892,7 @@
         <v>2</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>73</v>
@@ -8906,7 +8905,7 @@
         <v>2</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>73</v>
@@ -8919,7 +8918,7 @@
         <v>2</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P14" s="5" t="s">
         <v>273</v>
@@ -8932,7 +8931,7 @@
         <v>3</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T14" s="5" t="s">
         <v>274</v>
@@ -8945,7 +8944,7 @@
         <v>3</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X14" s="5" t="s">
         <v>285</v>
@@ -8973,7 +8972,7 @@
         <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>73</v>
@@ -8986,7 +8985,7 @@
         <v>2</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>20</v>
@@ -8999,7 +8998,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>20</v>
@@ -9012,7 +9011,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>286</v>
@@ -9025,7 +9024,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T15" s="5" t="s">
         <v>287</v>
@@ -9038,7 +9037,7 @@
         <v>3</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X15" s="5" t="s">
         <v>284</v>
@@ -9066,7 +9065,7 @@
         <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>73</v>
@@ -9079,7 +9078,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>73</v>
@@ -9092,7 +9091,7 @@
         <v>2</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>73</v>
@@ -9105,7 +9104,7 @@
         <v>2</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P16" s="5" t="s">
         <v>273</v>
@@ -9118,7 +9117,7 @@
         <v>3</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T16" s="5" t="s">
         <v>274</v>
@@ -9131,7 +9130,7 @@
         <v>3</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X16" s="5" t="s">
         <v>275</v>
@@ -9159,7 +9158,7 @@
         <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>73</v>
@@ -9172,7 +9171,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>73</v>
@@ -9185,7 +9184,7 @@
         <v>2</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>20</v>
@@ -9198,7 +9197,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P17" s="5" t="s">
         <v>273</v>
@@ -9211,7 +9210,7 @@
         <v>3</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T17" s="5" t="s">
         <v>281</v>
@@ -9224,7 +9223,7 @@
         <v>3</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X17" s="5" t="s">
         <v>288</v>
@@ -9252,7 +9251,7 @@
         <v>121</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>73</v>
@@ -9265,7 +9264,7 @@
         <v>2</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>20</v>
@@ -9278,7 +9277,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>73</v>
@@ -9291,7 +9290,7 @@
         <v>2</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P18" s="5" t="s">
         <v>273</v>
@@ -9304,7 +9303,7 @@
         <v>3</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T18" s="5" t="s">
         <v>274</v>
@@ -9317,7 +9316,7 @@
         <v>3</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X18" s="5" t="s">
         <v>283</v>
@@ -9345,7 +9344,7 @@
         <v>123</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>73</v>
@@ -9358,7 +9357,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>73</v>
@@ -9371,7 +9370,7 @@
         <v>2</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>73</v>
@@ -9384,7 +9383,7 @@
         <v>2</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P19" s="5" t="s">
         <v>278</v>
@@ -9397,7 +9396,7 @@
         <v>1.5</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T19" s="5" t="s">
         <v>276</v>
@@ -9410,7 +9409,7 @@
         <v>0</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X19" s="5" t="s">
         <v>283</v>
@@ -9438,7 +9437,7 @@
         <v>126</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>73</v>
@@ -9451,7 +9450,7 @@
         <v>2</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>73</v>
@@ -9464,7 +9463,7 @@
         <v>2</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>73</v>
@@ -9477,7 +9476,7 @@
         <v>2</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P20" s="5" t="s">
         <v>278</v>
@@ -9490,7 +9489,7 @@
         <v>1.5</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T20" s="5" t="s">
         <v>274</v>
@@ -9503,7 +9502,7 @@
         <v>3</v>
       </c>
       <c r="W20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X20" s="5" t="s">
         <v>289</v>
@@ -9531,7 +9530,7 @@
         <v>128</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>20</v>
@@ -9544,7 +9543,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>20</v>
@@ -9557,7 +9556,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>20</v>
@@ -9570,7 +9569,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>290</v>
@@ -9583,7 +9582,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T21" s="5" t="s">
         <v>205</v>
@@ -9596,7 +9595,7 @@
         <v>0</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="X21" s="5" t="s">
         <v>291</v>
@@ -9624,7 +9623,7 @@
         <v>131</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>73</v>
@@ -9637,7 +9636,7 @@
         <v>2</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>73</v>
@@ -9650,7 +9649,7 @@
         <v>2</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>20</v>
@@ -9663,7 +9662,7 @@
         <v>2</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>273</v>
@@ -9676,7 +9675,7 @@
         <v>3</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T22" s="5" t="s">
         <v>292</v>
@@ -9689,7 +9688,7 @@
         <v>3</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X22" s="5" t="s">
         <v>279</v>
@@ -9717,7 +9716,7 @@
         <v>133</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>73</v>
@@ -9730,7 +9729,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>73</v>
@@ -9743,7 +9742,7 @@
         <v>2</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>73</v>
@@ -9756,7 +9755,7 @@
         <v>2</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P23" s="5" t="s">
         <v>278</v>
@@ -9769,7 +9768,7 @@
         <v>1.5</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T23" s="5" t="s">
         <v>276</v>
@@ -9782,7 +9781,7 @@
         <v>0</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X23" s="5" t="s">
         <v>293</v>
@@ -9810,7 +9809,7 @@
         <v>135</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>73</v>
@@ -9823,7 +9822,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>73</v>
@@ -9836,7 +9835,7 @@
         <v>2</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>73</v>
@@ -9849,7 +9848,7 @@
         <v>2</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P24" s="5" t="s">
         <v>278</v>
@@ -9862,7 +9861,7 @@
         <v>1.5</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T24" s="5" t="s">
         <v>276</v>
@@ -9875,7 +9874,7 @@
         <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X24" s="5" t="s">
         <v>294</v>
@@ -9903,7 +9902,7 @@
         <v>137</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>73</v>
@@ -9916,7 +9915,7 @@
         <v>2</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>20</v>
@@ -9929,7 +9928,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>20</v>
@@ -9942,7 +9941,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P25" s="5" t="s">
         <v>278</v>
@@ -9955,7 +9954,7 @@
         <v>1.5</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T25" s="5" t="s">
         <v>274</v>
@@ -9968,7 +9967,7 @@
         <v>3</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X25" s="5" t="s">
         <v>279</v>
@@ -9996,7 +9995,7 @@
         <v>139</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>73</v>
@@ -10009,7 +10008,7 @@
         <v>2</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>73</v>
@@ -10022,7 +10021,7 @@
         <v>2</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L26" s="5" t="s">
         <v>73</v>
@@ -10035,7 +10034,7 @@
         <v>2</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P26" s="5" t="s">
         <v>273</v>
@@ -10048,7 +10047,7 @@
         <v>3</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T26" s="5" t="s">
         <v>281</v>
@@ -10061,7 +10060,7 @@
         <v>3</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X26" s="5" t="s">
         <v>283</v>
@@ -10089,7 +10088,7 @@
         <v>141</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>73</v>
@@ -10102,7 +10101,7 @@
         <v>2</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>73</v>
@@ -10115,7 +10114,7 @@
         <v>2</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L27" s="5" t="s">
         <v>20</v>
@@ -10128,7 +10127,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P27" s="5" t="s">
         <v>278</v>
@@ -10141,7 +10140,7 @@
         <v>1.5</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T27" s="5" t="s">
         <v>281</v>
@@ -10154,7 +10153,7 @@
         <v>3</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X27" s="5" t="s">
         <v>295</v>
@@ -10182,7 +10181,7 @@
         <v>143</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>20</v>
@@ -10195,7 +10194,7 @@
         <v>2</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>20</v>
@@ -10208,7 +10207,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>73</v>
@@ -10221,7 +10220,7 @@
         <v>2</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P28" s="5" t="s">
         <v>273</v>
@@ -10234,7 +10233,7 @@
         <v>3</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T28" s="5" t="s">
         <v>281</v>
@@ -10247,7 +10246,7 @@
         <v>3</v>
       </c>
       <c r="W28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X28" s="5" t="s">
         <v>279</v>
@@ -10275,7 +10274,7 @@
         <v>145</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>73</v>
@@ -10288,7 +10287,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>73</v>
@@ -10301,7 +10300,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>20</v>
@@ -10314,7 +10313,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="P29" s="5" t="s">
         <v>278</v>
@@ -10327,7 +10326,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T29" s="5" t="s">
         <v>274</v>
@@ -10340,7 +10339,7 @@
         <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="X29" s="5" t="s">
         <v>296</v>
@@ -10368,7 +10367,7 @@
         <v>148</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>73</v>
@@ -10381,7 +10380,7 @@
         <v>2</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>20</v>
@@ -10394,7 +10393,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>73</v>
@@ -10407,7 +10406,7 @@
         <v>2</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P30" s="5" t="s">
         <v>273</v>
@@ -10420,7 +10419,7 @@
         <v>3</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T30" s="5" t="s">
         <v>274</v>
@@ -10433,7 +10432,7 @@
         <v>3</v>
       </c>
       <c r="W30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X30" s="5" t="s">
         <v>289</v>
@@ -10461,7 +10460,7 @@
         <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>73</v>
@@ -10474,7 +10473,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>73</v>
@@ -10487,7 +10486,7 @@
         <v>2</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>73</v>
@@ -10500,7 +10499,7 @@
         <v>2</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P31" s="5" t="s">
         <v>278</v>
@@ -10513,7 +10512,7 @@
         <v>1.5</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T31" s="5" t="s">
         <v>274</v>
@@ -10526,7 +10525,7 @@
         <v>3</v>
       </c>
       <c r="W31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X31" s="5" t="s">
         <v>297</v>
@@ -10554,7 +10553,7 @@
         <v>152</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>73</v>
@@ -10567,7 +10566,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>73</v>
@@ -10580,7 +10579,7 @@
         <v>2</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>73</v>
@@ -10593,7 +10592,7 @@
         <v>2</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P32" s="5" t="s">
         <v>273</v>
@@ -10606,7 +10605,7 @@
         <v>3</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T32" s="5" t="s">
         <v>274</v>
@@ -10619,7 +10618,7 @@
         <v>3</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X32" s="5" t="s">
         <v>298</v>
@@ -10647,7 +10646,7 @@
         <v>154</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>155</v>
@@ -10660,7 +10659,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>155</v>
@@ -10673,7 +10672,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>155</v>
@@ -10686,7 +10685,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="P33" s="5" t="s">
         <v>155</v>
@@ -10699,7 +10698,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T33" s="5" t="s">
         <v>155</v>
@@ -10712,7 +10711,7 @@
         <v>0</v>
       </c>
       <c r="W33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="X33" s="5" t="s">
         <v>155</v>
@@ -10740,7 +10739,7 @@
         <v>157</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>20</v>
@@ -10753,7 +10752,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>20</v>
@@ -10766,7 +10765,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>20</v>
@@ -10779,7 +10778,7 @@
         <v>0</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="P34" s="5" t="s">
         <v>278</v>
@@ -10792,7 +10791,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T34" s="5" t="s">
         <v>276</v>
@@ -10805,7 +10804,7 @@
         <v>0</v>
       </c>
       <c r="W34" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="X34" s="5" t="s">
         <v>289</v>
@@ -11066,7 +11065,7 @@
         <v>98</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>311</v>
@@ -11079,7 +11078,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>312</v>
@@ -11107,7 +11106,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>313</v>
@@ -11120,7 +11119,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>314</v>
@@ -11148,7 +11147,7 @@
         <v>104</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>311</v>
@@ -11161,7 +11160,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>312</v>
@@ -11189,7 +11188,7 @@
         <v>106</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>315</v>
@@ -11202,7 +11201,7 @@
         <v>5</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>312</v>
@@ -11230,7 +11229,7 @@
         <v>108</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>313</v>
@@ -11243,7 +11242,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>312</v>
@@ -11271,7 +11270,7 @@
         <v>110</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>315</v>
@@ -11284,7 +11283,7 @@
         <v>5</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>312</v>
@@ -11312,7 +11311,7 @@
         <v>112</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>313</v>
@@ -11325,7 +11324,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>312</v>
@@ -11353,7 +11352,7 @@
         <v>114</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>315</v>
@@ -11366,7 +11365,7 @@
         <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>312</v>
@@ -11394,7 +11393,7 @@
         <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>311</v>
@@ -11407,7 +11406,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>312</v>
@@ -11435,7 +11434,7 @@
         <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>313</v>
@@ -11448,7 +11447,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>312</v>
@@ -11476,7 +11475,7 @@
         <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>311</v>
@@ -11489,7 +11488,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>314</v>
@@ -11517,7 +11516,7 @@
         <v>121</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>311</v>
@@ -11530,7 +11529,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>312</v>
@@ -11558,7 +11557,7 @@
         <v>123</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>315</v>
@@ -11571,7 +11570,7 @@
         <v>5</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>314</v>
@@ -11599,7 +11598,7 @@
         <v>126</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>313</v>
@@ -11612,7 +11611,7 @@
         <v>5</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>312</v>
@@ -11640,7 +11639,7 @@
         <v>128</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>311</v>
@@ -11653,7 +11652,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>206</v>
@@ -11681,7 +11680,7 @@
         <v>131</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>311</v>
@@ -11694,7 +11693,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>314</v>
@@ -11722,7 +11721,7 @@
         <v>133</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>315</v>
@@ -11735,7 +11734,7 @@
         <v>5</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>312</v>
@@ -11763,7 +11762,7 @@
         <v>135</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>311</v>
@@ -11776,7 +11775,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>312</v>
@@ -11804,7 +11803,7 @@
         <v>137</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>311</v>
@@ -11817,7 +11816,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>316</v>
@@ -11845,7 +11844,7 @@
         <v>139</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>315</v>
@@ -11858,7 +11857,7 @@
         <v>5</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>312</v>
@@ -11886,7 +11885,7 @@
         <v>141</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>315</v>
@@ -11899,7 +11898,7 @@
         <v>5</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>312</v>
@@ -11927,7 +11926,7 @@
         <v>143</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>313</v>
@@ -11940,7 +11939,7 @@
         <v>5</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>312</v>
@@ -11968,7 +11967,7 @@
         <v>145</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>315</v>
@@ -11981,7 +11980,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>314</v>
@@ -12009,7 +12008,7 @@
         <v>148</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>315</v>
@@ -12022,7 +12021,7 @@
         <v>5</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>312</v>
@@ -12050,7 +12049,7 @@
         <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>313</v>
@@ -12063,7 +12062,7 @@
         <v>5</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>317</v>
@@ -12091,7 +12090,7 @@
         <v>152</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>315</v>
@@ -12104,7 +12103,7 @@
         <v>5</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>312</v>
@@ -12132,7 +12131,7 @@
         <v>154</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>155</v>
@@ -12145,7 +12144,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>155</v>
@@ -12173,7 +12172,7 @@
         <v>157</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>311</v>
@@ -12186,7 +12185,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>314</v>
@@ -12610,7 +12609,7 @@
         <v>98</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>349</v>
@@ -12623,7 +12622,7 @@
         <v>5</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>350</v>
@@ -12636,7 +12635,7 @@
         <v>5</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>351</v>
@@ -12649,7 +12648,7 @@
         <v>5</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>352</v>
@@ -12662,7 +12661,7 @@
         <v>4</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>353</v>
@@ -12675,7 +12674,7 @@
         <v>2</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X7" s="5" t="s">
         <v>354</v>
@@ -12688,7 +12687,7 @@
         <v>0</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB7" s="5" t="s">
         <v>353</v>
@@ -12716,7 +12715,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>355</v>
@@ -12729,7 +12728,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>356</v>
@@ -12742,7 +12741,7 @@
         <v>2.5</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>357</v>
@@ -12755,7 +12754,7 @@
         <v>5</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>352</v>
@@ -12768,7 +12767,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T8" s="5" t="s">
         <v>353</v>
@@ -12781,7 +12780,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X8" s="5" t="s">
         <v>353</v>
@@ -12794,7 +12793,7 @@
         <v>0</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB8" s="5" t="s">
         <v>352</v>
@@ -12822,7 +12821,7 @@
         <v>104</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>355</v>
@@ -12835,7 +12834,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>350</v>
@@ -12848,7 +12847,7 @@
         <v>5</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>358</v>
@@ -12861,7 +12860,7 @@
         <v>5</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P9" s="5" t="s">
         <v>359</v>
@@ -12874,7 +12873,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>354</v>
@@ -12887,7 +12886,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X9" s="5" t="s">
         <v>354</v>
@@ -12900,7 +12899,7 @@
         <v>0</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB9" s="5" t="s">
         <v>353</v>
@@ -12928,7 +12927,7 @@
         <v>106</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>360</v>
@@ -12941,7 +12940,7 @@
         <v>5</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>350</v>
@@ -12954,7 +12953,7 @@
         <v>5</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>357</v>
@@ -12967,7 +12966,7 @@
         <v>5</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>361</v>
@@ -12980,7 +12979,7 @@
         <v>4</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T10" s="5" t="s">
         <v>353</v>
@@ -12993,7 +12992,7 @@
         <v>2</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X10" s="5" t="s">
         <v>353</v>
@@ -13006,7 +13005,7 @@
         <v>2</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB10" s="5" t="s">
         <v>359</v>
@@ -13034,7 +13033,7 @@
         <v>108</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>355</v>
@@ -13047,7 +13046,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>350</v>
@@ -13060,7 +13059,7 @@
         <v>5</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>362</v>
@@ -13073,7 +13072,7 @@
         <v>5</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>359</v>
@@ -13086,7 +13085,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T11" s="5" t="s">
         <v>353</v>
@@ -13099,7 +13098,7 @@
         <v>0</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X11" s="5" t="s">
         <v>353</v>
@@ -13112,7 +13111,7 @@
         <v>0</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB11" s="5" t="s">
         <v>354</v>
@@ -13140,7 +13139,7 @@
         <v>110</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>355</v>
@@ -13153,7 +13152,7 @@
         <v>5</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>350</v>
@@ -13166,7 +13165,7 @@
         <v>5</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>357</v>
@@ -13179,7 +13178,7 @@
         <v>5</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P12" s="5" t="s">
         <v>363</v>
@@ -13192,7 +13191,7 @@
         <v>4</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T12" s="5" t="s">
         <v>353</v>
@@ -13205,7 +13204,7 @@
         <v>2</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X12" s="5" t="s">
         <v>354</v>
@@ -13218,7 +13217,7 @@
         <v>2</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB12" s="5" t="s">
         <v>359</v>
@@ -13246,7 +13245,7 @@
         <v>112</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>355</v>
@@ -13259,7 +13258,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>350</v>
@@ -13272,7 +13271,7 @@
         <v>5</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>357</v>
@@ -13285,7 +13284,7 @@
         <v>5</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P13" s="5" t="s">
         <v>363</v>
@@ -13298,7 +13297,7 @@
         <v>4</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T13" s="5" t="s">
         <v>359</v>
@@ -13311,7 +13310,7 @@
         <v>2</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X13" s="5" t="s">
         <v>354</v>
@@ -13324,7 +13323,7 @@
         <v>2</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB13" s="5" t="s">
         <v>353</v>
@@ -13352,7 +13351,7 @@
         <v>114</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>355</v>
@@ -13365,7 +13364,7 @@
         <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>350</v>
@@ -13378,7 +13377,7 @@
         <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>357</v>
@@ -13391,7 +13390,7 @@
         <v>5</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P14" s="5" t="s">
         <v>352</v>
@@ -13404,7 +13403,7 @@
         <v>4</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T14" s="5" t="s">
         <v>352</v>
@@ -13417,7 +13416,7 @@
         <v>2</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X14" s="5" t="s">
         <v>352</v>
@@ -13430,7 +13429,7 @@
         <v>2</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB14" s="5" t="s">
         <v>359</v>
@@ -13458,7 +13457,7 @@
         <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>355</v>
@@ -13471,7 +13470,7 @@
         <v>5</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>350</v>
@@ -13484,7 +13483,7 @@
         <v>5</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>357</v>
@@ -13497,7 +13496,7 @@
         <v>5</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P15" s="5" t="s">
         <v>364</v>
@@ -13510,7 +13509,7 @@
         <v>4</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T15" s="5" t="s">
         <v>353</v>
@@ -13523,7 +13522,7 @@
         <v>2</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X15" s="5" t="s">
         <v>353</v>
@@ -13536,7 +13535,7 @@
         <v>2</v>
       </c>
       <c r="AA15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB15" s="5" t="s">
         <v>353</v>
@@ -13564,7 +13563,7 @@
         <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>365</v>
@@ -13577,7 +13576,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>350</v>
@@ -13590,7 +13589,7 @@
         <v>5</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>366</v>
@@ -13603,7 +13602,7 @@
         <v>5</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P16" s="5" t="s">
         <v>367</v>
@@ -13616,7 +13615,7 @@
         <v>4</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T16" s="5" t="s">
         <v>353</v>
@@ -13629,7 +13628,7 @@
         <v>2</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X16" s="5" t="s">
         <v>353</v>
@@ -13642,7 +13641,7 @@
         <v>2</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB16" s="5" t="s">
         <v>353</v>
@@ -13670,7 +13669,7 @@
         <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>355</v>
@@ -13683,7 +13682,7 @@
         <v>5</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>350</v>
@@ -13696,7 +13695,7 @@
         <v>5</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>351</v>
@@ -13709,7 +13708,7 @@
         <v>5</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P17" s="5" t="s">
         <v>363</v>
@@ -13722,7 +13721,7 @@
         <v>4</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T17" s="5" t="s">
         <v>353</v>
@@ -13735,7 +13734,7 @@
         <v>0</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X17" s="5" t="s">
         <v>353</v>
@@ -13748,7 +13747,7 @@
         <v>0</v>
       </c>
       <c r="AA17" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB17" s="5" t="s">
         <v>353</v>
@@ -13776,7 +13775,7 @@
         <v>121</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>368</v>
@@ -13789,7 +13788,7 @@
         <v>5</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>350</v>
@@ -13802,7 +13801,7 @@
         <v>5</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>369</v>
@@ -13815,7 +13814,7 @@
         <v>5</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P18" s="5" t="s">
         <v>352</v>
@@ -13828,7 +13827,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T18" s="5" t="s">
         <v>353</v>
@@ -13841,7 +13840,7 @@
         <v>2</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X18" s="5" t="s">
         <v>354</v>
@@ -13854,7 +13853,7 @@
         <v>0</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB18" s="5" t="s">
         <v>359</v>
@@ -13882,7 +13881,7 @@
         <v>123</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>368</v>
@@ -13895,7 +13894,7 @@
         <v>5</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>350</v>
@@ -13908,7 +13907,7 @@
         <v>5</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>357</v>
@@ -13921,7 +13920,7 @@
         <v>5</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P19" s="5" t="s">
         <v>363</v>
@@ -13934,7 +13933,7 @@
         <v>4</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T19" s="5" t="s">
         <v>353</v>
@@ -13947,7 +13946,7 @@
         <v>2</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X19" s="5" t="s">
         <v>354</v>
@@ -13960,7 +13959,7 @@
         <v>0</v>
       </c>
       <c r="AA19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB19" s="5" t="s">
         <v>353</v>
@@ -13988,7 +13987,7 @@
         <v>126</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>355</v>
@@ -14001,7 +14000,7 @@
         <v>5</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>350</v>
@@ -14014,7 +14013,7 @@
         <v>5</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>357</v>
@@ -14027,7 +14026,7 @@
         <v>5</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P20" s="5" t="s">
         <v>370</v>
@@ -14040,7 +14039,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T20" s="5" t="s">
         <v>354</v>
@@ -14053,7 +14052,7 @@
         <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X20" s="5" t="s">
         <v>354</v>
@@ -14066,7 +14065,7 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB20" s="5" t="s">
         <v>354</v>
@@ -14094,7 +14093,7 @@
         <v>128</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>371</v>
@@ -14107,7 +14106,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>206</v>
@@ -14120,7 +14119,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>372</v>
@@ -14133,7 +14132,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>354</v>
@@ -14146,7 +14145,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T21" s="5" t="s">
         <v>354</v>
@@ -14159,7 +14158,7 @@
         <v>0</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X21" s="5" t="s">
         <v>354</v>
@@ -14172,7 +14171,7 @@
         <v>0</v>
       </c>
       <c r="AA21" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AB21" s="5" t="s">
         <v>354</v>
@@ -14200,7 +14199,7 @@
         <v>131</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>355</v>
@@ -14213,7 +14212,7 @@
         <v>5</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>350</v>
@@ -14226,7 +14225,7 @@
         <v>5</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>373</v>
@@ -14239,7 +14238,7 @@
         <v>5</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P22" s="5" t="s">
         <v>359</v>
@@ -14252,7 +14251,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T22" s="5" t="s">
         <v>353</v>
@@ -14265,7 +14264,7 @@
         <v>2</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X22" s="5" t="s">
         <v>353</v>
@@ -14278,7 +14277,7 @@
         <v>2</v>
       </c>
       <c r="AA22" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB22" s="5" t="s">
         <v>353</v>
@@ -14306,7 +14305,7 @@
         <v>133</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>355</v>
@@ -14319,7 +14318,7 @@
         <v>5</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>350</v>
@@ -14332,7 +14331,7 @@
         <v>5</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>374</v>
@@ -14345,7 +14344,7 @@
         <v>5</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P23" s="5" t="s">
         <v>352</v>
@@ -14358,7 +14357,7 @@
         <v>4</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T23" s="5" t="s">
         <v>353</v>
@@ -14371,7 +14370,7 @@
         <v>2</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X23" s="5" t="s">
         <v>353</v>
@@ -14384,7 +14383,7 @@
         <v>2</v>
       </c>
       <c r="AA23" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB23" s="5" t="s">
         <v>354</v>
@@ -14412,7 +14411,7 @@
         <v>135</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>355</v>
@@ -14425,7 +14424,7 @@
         <v>5</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>350</v>
@@ -14438,7 +14437,7 @@
         <v>5</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>375</v>
@@ -14451,7 +14450,7 @@
         <v>5</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P24" s="5" t="s">
         <v>364</v>
@@ -14464,7 +14463,7 @@
         <v>4</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T24" s="5" t="s">
         <v>353</v>
@@ -14477,7 +14476,7 @@
         <v>2</v>
       </c>
       <c r="W24" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X24" s="5" t="s">
         <v>353</v>
@@ -14490,7 +14489,7 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB24" s="5" t="s">
         <v>353</v>
@@ -14518,7 +14517,7 @@
         <v>137</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>368</v>
@@ -14531,7 +14530,7 @@
         <v>5</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>350</v>
@@ -14544,7 +14543,7 @@
         <v>5</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>376</v>
@@ -14557,7 +14556,7 @@
         <v>5</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P25" s="5" t="s">
         <v>353</v>
@@ -14570,7 +14569,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T25" s="5" t="s">
         <v>353</v>
@@ -14583,7 +14582,7 @@
         <v>0</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X25" s="5" t="s">
         <v>353</v>
@@ -14596,7 +14595,7 @@
         <v>0</v>
       </c>
       <c r="AA25" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB25" s="5" t="s">
         <v>354</v>
@@ -14624,7 +14623,7 @@
         <v>139</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>355</v>
@@ -14637,7 +14636,7 @@
         <v>5</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>350</v>
@@ -14650,7 +14649,7 @@
         <v>5</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L26" s="5" t="s">
         <v>377</v>
@@ -14663,7 +14662,7 @@
         <v>5</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P26" s="5" t="s">
         <v>367</v>
@@ -14676,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T26" s="5" t="s">
         <v>353</v>
@@ -14689,7 +14688,7 @@
         <v>0</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X26" s="5" t="s">
         <v>353</v>
@@ -14702,7 +14701,7 @@
         <v>0</v>
       </c>
       <c r="AA26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB26" s="5" t="s">
         <v>359</v>
@@ -14730,7 +14729,7 @@
         <v>141</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>368</v>
@@ -14743,7 +14742,7 @@
         <v>5</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>350</v>
@@ -14756,7 +14755,7 @@
         <v>5</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L27" s="5" t="s">
         <v>378</v>
@@ -14769,7 +14768,7 @@
         <v>5</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P27" s="5" t="s">
         <v>353</v>
@@ -14782,7 +14781,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T27" s="5" t="s">
         <v>354</v>
@@ -14795,7 +14794,7 @@
         <v>0</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X27" s="5" t="s">
         <v>354</v>
@@ -14808,7 +14807,7 @@
         <v>0</v>
       </c>
       <c r="AA27" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB27" s="5" t="s">
         <v>352</v>
@@ -14836,7 +14835,7 @@
         <v>143</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>355</v>
@@ -14849,7 +14848,7 @@
         <v>5</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>379</v>
@@ -14862,7 +14861,7 @@
         <v>2.5</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>357</v>
@@ -14875,7 +14874,7 @@
         <v>5</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P28" s="5" t="s">
         <v>359</v>
@@ -14888,7 +14887,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T28" s="5" t="s">
         <v>353</v>
@@ -14901,7 +14900,7 @@
         <v>2</v>
       </c>
       <c r="W28" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X28" s="5" t="s">
         <v>354</v>
@@ -14914,7 +14913,7 @@
         <v>0</v>
       </c>
       <c r="AA28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB28" s="5" t="s">
         <v>354</v>
@@ -14942,7 +14941,7 @@
         <v>145</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>368</v>
@@ -14955,7 +14954,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>379</v>
@@ -14968,7 +14967,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>369</v>
@@ -14981,7 +14980,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P29" s="5" t="s">
         <v>359</v>
@@ -14994,7 +14993,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T29" s="5" t="s">
         <v>353</v>
@@ -15007,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X29" s="5" t="s">
         <v>353</v>
@@ -15020,7 +15019,7 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AB29" s="5" t="s">
         <v>359</v>
@@ -15048,7 +15047,7 @@
         <v>148</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>368</v>
@@ -15061,7 +15060,7 @@
         <v>5</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>350</v>
@@ -15074,7 +15073,7 @@
         <v>5</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>380</v>
@@ -15087,7 +15086,7 @@
         <v>5</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P30" s="5" t="s">
         <v>353</v>
@@ -15100,7 +15099,7 @@
         <v>4</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T30" s="5" t="s">
         <v>353</v>
@@ -15113,7 +15112,7 @@
         <v>2</v>
       </c>
       <c r="W30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X30" s="5" t="s">
         <v>353</v>
@@ -15126,7 +15125,7 @@
         <v>2</v>
       </c>
       <c r="AA30" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB30" s="5" t="s">
         <v>354</v>
@@ -15154,7 +15153,7 @@
         <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>355</v>
@@ -15167,7 +15166,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>350</v>
@@ -15180,7 +15179,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>357</v>
@@ -15193,7 +15192,7 @@
         <v>0</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P31" s="5" t="s">
         <v>352</v>
@@ -15206,7 +15205,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T31" s="5" t="s">
         <v>353</v>
@@ -15219,7 +15218,7 @@
         <v>2</v>
       </c>
       <c r="W31" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X31" s="5" t="s">
         <v>353</v>
@@ -15232,7 +15231,7 @@
         <v>0</v>
       </c>
       <c r="AA31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB31" s="5" t="s">
         <v>353</v>
@@ -15260,7 +15259,7 @@
         <v>152</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>355</v>
@@ -15273,7 +15272,7 @@
         <v>5</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>350</v>
@@ -15286,7 +15285,7 @@
         <v>5</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>381</v>
@@ -15299,7 +15298,7 @@
         <v>5</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P32" s="5" t="s">
         <v>382</v>
@@ -15312,7 +15311,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T32" s="5" t="s">
         <v>359</v>
@@ -15325,7 +15324,7 @@
         <v>2</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X32" s="5" t="s">
         <v>354</v>
@@ -15338,7 +15337,7 @@
         <v>2</v>
       </c>
       <c r="AA32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AB32" s="5" t="s">
         <v>353</v>
@@ -15366,7 +15365,7 @@
         <v>154</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>155</v>
@@ -15379,7 +15378,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>155</v>
@@ -15392,7 +15391,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>155</v>
@@ -15405,7 +15404,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P33" s="5" t="s">
         <v>155</v>
@@ -15418,7 +15417,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T33" s="5" t="s">
         <v>155</v>
@@ -15431,7 +15430,7 @@
         <v>0</v>
       </c>
       <c r="W33" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X33" s="5" t="s">
         <v>155</v>
@@ -15444,7 +15443,7 @@
         <v>0</v>
       </c>
       <c r="AA33" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AB33" s="5" t="s">
         <v>155</v>
@@ -15472,7 +15471,7 @@
         <v>157</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>383</v>
@@ -15485,7 +15484,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>350</v>
@@ -15498,7 +15497,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>378</v>
@@ -15511,7 +15510,7 @@
         <v>0</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P34" s="5" t="s">
         <v>359</v>
@@ -15524,7 +15523,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T34" s="5" t="s">
         <v>353</v>
@@ -15537,7 +15536,7 @@
         <v>0</v>
       </c>
       <c r="W34" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="X34" s="5" t="s">
         <v>354</v>
@@ -15550,7 +15549,7 @@
         <v>0</v>
       </c>
       <c r="AA34" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AB34" s="5" t="s">
         <v>353</v>
@@ -18202,36 +18201,36 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O7:O34">
-    <cfRule type="expression" dxfId="8" priority="27">
-      <formula>O7="Sem evidência"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="25">
+    <cfRule type="expression" dxfId="8" priority="25">
       <formula>O7="Sim"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="26">
+    <cfRule type="expression" dxfId="7" priority="26">
       <formula>O7="Não"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="27">
+      <formula>O7="Sem evidência"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R7:R34">
-    <cfRule type="expression" dxfId="5" priority="15">
-      <formula>R7="Sem evidência"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="13">
+    <cfRule type="expression" dxfId="5" priority="13">
       <formula>R7="Sim"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="14">
+    <cfRule type="expression" dxfId="4" priority="14">
       <formula>R7="Não"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="15">
+      <formula>R7="Sem evidência"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U7:U34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>U7="Sim"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>U7="Não"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>U7="Sem evidência"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>U7="Sim"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/DADOS.xlsx
+++ b/DADOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://justicagovbr-my.sharepoint.com/personal/marcelo_cortez_mj_gov_br1/Documents/1. SENAPPEN/2. OUVIDORIA/GITHUB/PARAMETROS MINIMOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="523" documentId="11_C2318B871671820C540791CC0C0EFCB85A7F69AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDBF98C4-2906-4A1F-8597-21E0CDC6E6F6}"/>
+  <xr:revisionPtr revIDLastSave="525" documentId="11_C2318B871671820C540791CC0C0EFCB85A7F69AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67BFA272-BA4A-4042-BCB2-163FBB162495}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Metodologia" sheetId="1" r:id="rId1"/>
